--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.6981577220176</v>
+        <v>5.15095062982786</v>
       </c>
       <c r="D2" t="n">
-        <v>33.36437138623009</v>
+        <v>5.42171035026239</v>
       </c>
       <c r="E2" t="n">
-        <v>10.53909347590399</v>
+        <v>1.712602689834398</v>
       </c>
       <c r="F2" t="n">
-        <v>10.28366599224863</v>
+        <v>1.671095723740402</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.91722092707278</v>
+        <v>6.161548400649326</v>
       </c>
       <c r="D3" t="n">
-        <v>39.37029608788956</v>
+        <v>6.397673114282053</v>
       </c>
       <c r="E3" t="n">
-        <v>10.53909347590399</v>
+        <v>1.712602689834398</v>
       </c>
       <c r="F3" t="n">
-        <v>10.28366599224863</v>
+        <v>1.671095723740402</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.89800107230745</v>
+        <v>9.733425174249961</v>
       </c>
       <c r="D4" t="n">
-        <v>60.52096221156708</v>
+        <v>9.83465635937965</v>
       </c>
       <c r="E4" t="n">
-        <v>10.53909347590399</v>
+        <v>1.712602689834398</v>
       </c>
       <c r="F4" t="n">
-        <v>10.28366599224863</v>
+        <v>1.671095723740402</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.52056792378658</v>
+        <v>6.58459228761532</v>
       </c>
       <c r="D5" t="n">
-        <v>39.79285646251756</v>
+        <v>6.466339175159104</v>
       </c>
       <c r="E5" t="n">
-        <v>10.53909347590399</v>
+        <v>1.712602689834398</v>
       </c>
       <c r="F5" t="n">
-        <v>10.28366599224863</v>
+        <v>1.671095723740402</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
